--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,6 +456,19 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,19 @@
       </c>
       <c r="C4" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,6 +483,19 @@
       </c>
       <c r="C5" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" t="n">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,6 +511,19 @@
         <v>67</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,6 +524,19 @@
         <v>85</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,6 +563,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>50</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +576,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,6 +589,19 @@
         <v>63</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,6 +602,19 @@
         <v>74</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,19 @@
         <v>73</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,6 +628,19 @@
         <v>65</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -641,6 +641,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,6 +654,19 @@
         <v>82</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,19 @@
         <v>98</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,19 @@
         <v>81</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,6 +693,19 @@
         <v>88</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -706,6 +706,19 @@
         <v>77</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,6 +719,19 @@
         <v>71</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,6 +732,19 @@
         <v>65</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,6 +745,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,6 +758,19 @@
         <v>99</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,6 +771,19 @@
         <v>56</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,19 @@
         <v>83</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,6 +797,19 @@
         <v>64</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,6 +810,19 @@
         <v>49</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -823,6 +823,19 @@
         <v>68</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,6 +836,19 @@
         <v>68</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -849,6 +849,19 @@
         <v>69</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -862,6 +862,19 @@
         <v>74</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,19 @@
         <v>74</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,6 +888,19 @@
         <v>88</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,19 @@
         <v>96</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C39"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,6 +927,19 @@
         <v>84</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -940,6 +940,19 @@
         <v>95</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -953,6 +953,19 @@
         <v>75</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,6 +966,19 @@
         <v>58</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,19 @@
         <v>87</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,6 +992,19 @@
         <v>116</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,6 +1005,19 @@
         <v>112</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1018,6 +1018,19 @@
         <v>105</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,6 +1031,19 @@
         <v>111</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="n">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,19 @@
         <v>72</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,6 +1057,19 @@
         <v>77</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1070,6 +1070,19 @@
         <v>72</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1083,6 +1083,19 @@
         <v>64</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1096,6 +1096,19 @@
         <v>68</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,6 +1109,19 @@
         <v>80</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1122,6 +1122,19 @@
         <v>71</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,6 +1135,19 @@
         <v>90</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,6 +1148,19 @@
         <v>90</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1161,6 +1161,19 @@
         <v>119</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,6 +1174,19 @@
         <v>68</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="n">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1187,6 +1187,19 @@
         <v>96</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,6 +1200,19 @@
         <v>127</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,6 +1213,19 @@
         <v>149</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1226,6 +1226,19 @@
         <v>129</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C63"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1239,6 +1239,19 @@
         <v>57</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,6 +1252,19 @@
         <v>61</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,6 +1265,19 @@
         <v>67</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,6 +1278,19 @@
         <v>66</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="n">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,19 @@
         <v>83</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="n">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,6 +1304,19 @@
         <v>109</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1317,6 +1317,19 @@
         <v>136</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="n">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1330,6 +1330,19 @@
         <v>101</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1343,6 +1343,19 @@
         <v>135</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C72"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1356,6 +1356,19 @@
         <v>100</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="n">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,6 +1369,19 @@
         <v>101</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1382,6 +1382,19 @@
         <v>66</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1395,19 @@
         <v>104</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1408,6 +1408,19 @@
         <v>87</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,6 +1421,19 @@
         <v>96</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1434,6 +1434,19 @@
         <v>116</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1447,6 +1447,19 @@
         <v>85</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1460,6 +1460,19 @@
         <v>123</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1473,6 +1473,19 @@
         <v>95</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C82"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1486,6 +1486,19 @@
         <v>80</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" t="n">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1499,6 +1499,19 @@
         <v>55</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="n">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1512,6 +1512,19 @@
         <v>84</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="n">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1525,6 +1525,19 @@
         <v>110</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="n">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1538,6 +1538,19 @@
         <v>140</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="n">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1551,6 +1551,19 @@
         <v>134</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="n">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1564,6 +1564,19 @@
         <v>159</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="n">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1577,6 +1577,19 @@
         <v>127</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="n">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1590,6 +1590,19 @@
         <v>126</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1603,6 +1603,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="n">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1616,6 +1616,19 @@
         <v>97</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="n">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1629,6 +1629,19 @@
         <v>104</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="n">
+        <v>124</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,6 +1642,19 @@
         <v>124</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="n">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1655,6 +1655,19 @@
         <v>113</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="n">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1668,6 +1668,19 @@
         <v>114</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="n">
+        <v>117</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1681,6 +1681,19 @@
         <v>117</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="n">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,6 +1694,19 @@
         <v>76</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="n">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,6 +1707,19 @@
         <v>106</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="n">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1720,6 +1720,19 @@
         <v>72</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="n">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1733,6 +1733,19 @@
         <v>67</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="n">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1746,6 +1746,19 @@
         <v>87</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" t="n">
+        <v>99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C103"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1759,6 +1759,19 @@
         <v>99</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="n">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1772,6 +1772,19 @@
         <v>89</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" t="n">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,6 +1785,19 @@
         <v>123</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" t="n">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,6 +1798,19 @@
         <v>106</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1811,6 +1811,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1824,6 +1824,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1837,6 +1837,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1850,6 +1850,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1863,6 +1863,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C112"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1876,6 +1876,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C113"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1889,6 +1889,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1902,6 +1902,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C115"/>
+  <dimension ref="A1:C116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1915,6 +1915,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1928,6 +1928,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1941,6 +1941,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" t="n">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C118"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1954,6 +1954,19 @@
         <v>113</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" t="n">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,6 +1967,19 @@
         <v>91</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" t="n">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C120"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1980,6 +1980,19 @@
         <v>92</v>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1993,6 +1993,19 @@
         <v>95</v>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" t="n">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2006,6 +2006,19 @@
         <v>98</v>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,6 +2019,19 @@
         <v>107</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" t="n">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2032,6 +2032,19 @@
         <v>143</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" t="n">
+        <v>67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C125"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2045,6 +2045,19 @@
         <v>67</v>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" t="n">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C126"/>
+  <dimension ref="A1:C127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2058,6 +2058,19 @@
         <v>96</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" t="n">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C127"/>
+  <dimension ref="A1:C128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2071,6 +2071,19 @@
         <v>84</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" t="n">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2084,6 +2084,19 @@
         <v>77</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" t="n">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2097,6 +2097,19 @@
         <v>94</v>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0</v>
+      </c>
+      <c r="C130" t="n">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C130"/>
+  <dimension ref="A1:C131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2110,6 +2110,19 @@
         <v>121</v>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" t="n">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2123,6 +2123,19 @@
         <v>153</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" t="n">
+        <v>141</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2136,6 +2136,19 @@
         <v>141</v>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" t="n">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C133"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2149,6 +2149,19 @@
         <v>136</v>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" t="n">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +2162,19 @@
         <v>125</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
+      <c r="C135" t="n">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2175,6 +2175,19 @@
         <v>107</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
+      <c r="C136" t="n">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C136"/>
+  <dimension ref="A1:C137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2188,6 +2188,19 @@
         <v>96</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2201,6 +2201,19 @@
         <v>0</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" t="n">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2214,6 +2214,19 @@
         <v>129</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" t="n">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C139"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,6 +2227,19 @@
         <v>127</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" t="n">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2240,6 +2240,19 @@
         <v>72</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" t="n">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/anoto_amazon_data.xlsx
+++ b/data/anoto_amazon_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2253,6 +2253,19 @@
         <v>72</v>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>0</v>
+      </c>
+      <c r="C142" t="n">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
